--- a/branches/ig-publisher-migration/observations-summary.xlsx
+++ b/branches/ig-publisher-migration/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Profile</t>
   </si>
@@ -59,7 +59,10 @@
     <t/>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-laboratory-pathology-observations-uv-ips|2.0.1 (preferred)</t>
+    <t>null#null</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
     <t>dateTimeĵ</t>
@@ -254,19 +257,19 @@
         <v>14</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s" s="2">
         <v>14</v>
